--- a/maintenance/GuidePulley_TensionGauge_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/GuidePulley_TensionGauge_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,26 @@
           <t>Last_Done_Draw</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Required Parts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Planning months</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Estimated duration min</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -619,6 +639,22 @@
         <v>0</v>
       </c>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Bearing set; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -704,6 +740,18 @@
         <v>0</v>
       </c>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +831,22 @@
         <v>0</v>
       </c>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Load cell service/replacement</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>On-Condition</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/maintenance/GuidePulley_TensionGauge_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/GuidePulley_TensionGauge_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,22 +536,42 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Required Parts</t>
+          <t>Required_Parts</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Task_Group</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Planning months</t>
+          <t>Planning_Window_Months</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Estimated duration min</t>
+          <t>Est_Duration_Min</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Task_Groups</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV1</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV2</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_Furnace</t>
         </is>
       </c>
     </row>
@@ -594,7 +614,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>weeks</t>
@@ -626,22 +645,17 @@
           <t>PPE required. Methanol is toxic and can be absorbed through skin on prolonged exposure; wear impermeable gloves. Take care not to overload the load cell when cleaning.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
+          <t>2026-04-02</t>
+        </is>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Bearing set; IPA wipes / cleaning cloth</t>
+          <t>Bearing set, IPA wipes - small</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -695,7 +709,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>months</t>
@@ -727,20 +740,14 @@
           <t>PPE required. Working at height precautions: stay behind guard rails and/or use safety harness; good housekeeping to prevent items falling from the tower.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
+          <t>2026-02-26</t>
+        </is>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Monthly</t>
@@ -792,9 +799,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>Guide Pulley &amp; Tension Gauge (SG Controls)</t>
@@ -818,19 +822,20 @@
           <t>Do not attempt to disassemble the load cell.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U4" t="n">
+        <v>93</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>Load cell service/replacement</t>
@@ -846,6 +851,15 @@
       </c>
       <c r="Y4" t="n">
         <v>60</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1009</v>
       </c>
     </row>
   </sheetData>
